--- a/src/main/resources/templates/report/template.xlsx
+++ b/src/main/resources/templates/report/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shingo/develop/sandbox/etc/jxls-sample/src/main/resources/templates/report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9812EBA-6C69-A140-ABDE-C20A69537A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EDCC8F-BBE8-3C43-A329-0639178730E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{B3EC2514-B971-AE46-BD81-23E6E6792030}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="6" xr2:uid="{B3EC2514-B971-AE46-BD81-23E6E6792030}"/>
   </bookViews>
   <sheets>
     <sheet name="basic" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="each+if" sheetId="3" r:id="rId4"/>
     <sheet name="カスタムコマンド" sheetId="6" r:id="rId5"/>
     <sheet name="each-multisheet" sheetId="7" r:id="rId6"/>
+    <sheet name="条件付き書式" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -204,8 +205,35 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={77D37C28-EEF8-F846-A6E8-C350C7790E4C}</author>
+    <author>tc={1397B64E-7D58-5040-A28C-437B66ADB699}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{77D37C28-EEF8-F846-A6E8-C350C7790E4C}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    jx:area(lastCell="C100")</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="1" shapeId="0" xr:uid="{1397B64E-7D58-5040-A28C-437B66ADB699}">
+      <text>
+        <t>[スレッド化されたコメント]
+使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
+コメント:
+    jx:each(items="details" var="detail" lastCell="C5")</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>${text}</t>
     <phoneticPr fontId="2"/>
@@ -324,6 +352,54 @@
   </si>
   <si>
     <t>ID</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>条件付き書式</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウケn</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>条件付き書式の条件に数式を使用する際、直接セル参照を記述してしまうと、jx:eachでセルを複製する際に条件付き書式の条件の数式が"そのまま"複製されてしまう。
+しかし、セル参照をINDIRECTで代用することで回避できる。</t>
+    <rPh sb="0" eb="1">
+      <t>ジョウケn</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t xml:space="preserve">ジョウケン </t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チョクセテ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>キジュテゥ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>フクセイ</t>
+    </rPh>
+    <rPh sb="52" eb="55">
+      <t>ジョウケンテ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>フクセイ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ダイヨウ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>カイヒ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -369,14 +445,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Yu Gothic UI"/>
-    </font>
-    <font>
       <b/>
       <u/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="3"/>
@@ -415,7 +494,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -425,7 +504,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
@@ -440,12 +519,28 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="通貨" xfId="1" builtinId="7"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -861,6 +956,17 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment7.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A1" dT="2024-09-21T09:10:15.95" personId="{8AB23D77-E043-734E-AE6D-30910920CD93}" id="{77D37C28-EEF8-F846-A6E8-C350C7790E4C}">
+    <text>jx:area(lastCell="C100")</text>
+  </threadedComment>
+  <threadedComment ref="A5" dT="2024-09-21T09:12:08.29" personId="{8AB23D77-E043-734E-AE6D-30910920CD93}" id="{1397B64E-7D58-5040-A28C-437B66ADB699}">
+    <text>jx:each(items="details" var="detail" lastCell="C5")</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77443270-C9B0-9E4B-8E1E-3AD42A447BDB}">
   <dimension ref="A1:A10"/>
@@ -1040,7 +1146,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A4:C4 A6:C6">
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>MOD($A4,2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1119,4 +1225,67 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54D3857E-F115-F247-B969-A0E22B943575}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="1" width="5.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="61" customHeight="1">
+      <c r="A2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="8"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="A5:C5">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(INDIRECT(ADDRESS(ROW(),1)),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>